--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/110.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/110.xlsx
@@ -426,13 +426,13 @@
         <v>6.495117727418539</v>
       </c>
       <c r="E2">
-        <v>-10.0481379543732</v>
+        <v>-8.280230758726704</v>
       </c>
       <c r="F2">
-        <v>-5.509291987540612</v>
+        <v>-6.212329887398761</v>
       </c>
       <c r="G2">
-        <v>-3.370722333338605</v>
+        <v>-3.746605950302354</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>6.461924200954735</v>
       </c>
       <c r="E3">
-        <v>-9.880213081220765</v>
+        <v>-11.03379654993471</v>
       </c>
       <c r="F3">
-        <v>-5.546029253487367</v>
+        <v>-6.383332255460871</v>
       </c>
       <c r="G3">
-        <v>-3.707070511732605</v>
+        <v>-5.218391318348162</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>6.433750445443625</v>
       </c>
       <c r="E4">
-        <v>-11.21600423010734</v>
+        <v>-12.80927082564802</v>
       </c>
       <c r="F4">
-        <v>-5.611581279540504</v>
+        <v>-6.180675483835583</v>
       </c>
       <c r="G4">
-        <v>-3.872125799837352</v>
+        <v>-4.034031115245033</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>6.422296059962057</v>
       </c>
       <c r="E5">
-        <v>-10.74921818634469</v>
+        <v>-12.12148619336305</v>
       </c>
       <c r="F5">
-        <v>-5.294105330580579</v>
+        <v>-6.591012247016735</v>
       </c>
       <c r="G5">
-        <v>-3.897207457437748</v>
+        <v>-4.930510063608721</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>6.429220317947051</v>
       </c>
       <c r="E6">
-        <v>-12.1353342668785</v>
+        <v>-14.04868699070335</v>
       </c>
       <c r="F6">
-        <v>-5.475966766925988</v>
+        <v>-5.791570605555585</v>
       </c>
       <c r="G6">
-        <v>-3.389002018646272</v>
+        <v>-5.381855213996579</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>6.470258631635617</v>
       </c>
       <c r="E7">
-        <v>-12.72862323204542</v>
+        <v>-11.98745694815803</v>
       </c>
       <c r="F7">
-        <v>-5.190026764990641</v>
+        <v>-6.256737835495439</v>
       </c>
       <c r="G7">
-        <v>-3.256667071932307</v>
+        <v>-5.22774279979258</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>6.556656069204725</v>
       </c>
       <c r="E8">
-        <v>-12.65611783470861</v>
+        <v>-14.29278532513881</v>
       </c>
       <c r="F8">
-        <v>-5.209870306124703</v>
+        <v>-6.171086302780776</v>
       </c>
       <c r="G8">
-        <v>-3.642528883658327</v>
+        <v>-5.120036702103807</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>6.686417583897545</v>
       </c>
       <c r="E9">
-        <v>-13.55566296854026</v>
+        <v>-14.32203021028034</v>
       </c>
       <c r="F9">
-        <v>-5.244930128080789</v>
+        <v>-6.264712528482191</v>
       </c>
       <c r="G9">
-        <v>-3.251761645700937</v>
+        <v>-4.396386255719191</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>6.860733212415469</v>
       </c>
       <c r="E10">
-        <v>-14.60537682894028</v>
+        <v>-14.64791278529432</v>
       </c>
       <c r="F10">
-        <v>-5.066652209119891</v>
+        <v>-5.673808238838802</v>
       </c>
       <c r="G10">
-        <v>-3.11542360868445</v>
+        <v>-4.36708494719335</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>7.084045895922515</v>
       </c>
       <c r="E11">
-        <v>-15.41805224588279</v>
+        <v>-14.15142448051537</v>
       </c>
       <c r="F11">
-        <v>-5.008159530073412</v>
+        <v>-5.464309152466391</v>
       </c>
       <c r="G11">
-        <v>-3.561515523355637</v>
+        <v>-3.957152094107243</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>7.346424366151917</v>
       </c>
       <c r="E12">
-        <v>-15.54024406003176</v>
+        <v>-15.44355661149399</v>
       </c>
       <c r="F12">
-        <v>-5.193282248883643</v>
+        <v>-5.51620057167996</v>
       </c>
       <c r="G12">
-        <v>-2.691998372545906</v>
+        <v>-4.677271946093897</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>7.629409092928795</v>
       </c>
       <c r="E13">
-        <v>-16.2967890416492</v>
+        <v>-16.55536037901317</v>
       </c>
       <c r="F13">
-        <v>-4.881648775215663</v>
+        <v>-5.653451109915005</v>
       </c>
       <c r="G13">
-        <v>-2.890020093658395</v>
+        <v>-3.696255605472675</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>7.925292931207545</v>
       </c>
       <c r="E14">
-        <v>-17.1366126602677</v>
+        <v>-16.26105032478067</v>
       </c>
       <c r="F14">
-        <v>-4.609648539934626</v>
+        <v>-4.971216829010762</v>
       </c>
       <c r="G14">
-        <v>-2.753222685623586</v>
+        <v>-3.704242098748364</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>8.212508627201325</v>
       </c>
       <c r="E15">
-        <v>-17.89849218426617</v>
+        <v>-17.59536971961474</v>
       </c>
       <c r="F15">
-        <v>-4.337456123416139</v>
+        <v>-5.596072585025291</v>
       </c>
       <c r="G15">
-        <v>-2.296401176453013</v>
+        <v>-2.435301847507427</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>8.46144726658981</v>
       </c>
       <c r="E16">
-        <v>-18.97233828265306</v>
+        <v>-19.31536113178608</v>
       </c>
       <c r="F16">
-        <v>-4.058677357677993</v>
+        <v>-4.463836824591649</v>
       </c>
       <c r="G16">
-        <v>-1.626520107763018</v>
+        <v>-3.952197449552482</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>8.660867700410144</v>
       </c>
       <c r="E17">
-        <v>-20.46277681890158</v>
+        <v>-19.64756092804076</v>
       </c>
       <c r="F17">
-        <v>-3.801601817893195</v>
+        <v>-4.43404044911295</v>
       </c>
       <c r="G17">
-        <v>-2.290183261597866</v>
+        <v>-3.324978823578387</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>8.79725453158906</v>
       </c>
       <c r="E18">
-        <v>-20.19706407802751</v>
+        <v>-20.52592186046453</v>
       </c>
       <c r="F18">
-        <v>-3.771071508895616</v>
+        <v>-4.515948589534363</v>
       </c>
       <c r="G18">
-        <v>-1.439077044958179</v>
+        <v>-3.292583323121989</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>8.852961149255091</v>
       </c>
       <c r="E19">
-        <v>-20.91616763654953</v>
+        <v>-23.06661767399398</v>
       </c>
       <c r="F19">
-        <v>-3.147251212134587</v>
+        <v>-3.949305524384166</v>
       </c>
       <c r="G19">
-        <v>-1.889129394051617</v>
+        <v>-2.886893089512244</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>8.829612858079861</v>
       </c>
       <c r="E20">
-        <v>-22.54995048903685</v>
+        <v>-22.98597460886538</v>
       </c>
       <c r="F20">
-        <v>-2.835027112508411</v>
+        <v>-3.206111686307909</v>
       </c>
       <c r="G20">
-        <v>-1.917803989259604</v>
+        <v>-2.89028915382627</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>8.733497073544706</v>
       </c>
       <c r="E21">
-        <v>-22.75592360080172</v>
+        <v>-23.92089618164496</v>
       </c>
       <c r="F21">
-        <v>-2.152159130541028</v>
+        <v>-3.721543421882234</v>
       </c>
       <c r="G21">
-        <v>-1.503418518517331</v>
+        <v>-2.670309498037977</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>8.5676687667543</v>
       </c>
       <c r="E22">
-        <v>-22.56910140561528</v>
+        <v>-23.24186056114281</v>
       </c>
       <c r="F22">
-        <v>-1.865202721802445</v>
+        <v>-2.951054877883732</v>
       </c>
       <c r="G22">
-        <v>-1.733993238721071</v>
+        <v>-3.421400800324229</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>8.344223960054324</v>
       </c>
       <c r="E23">
-        <v>-23.7825331868146</v>
+        <v>-24.96563324911054</v>
       </c>
       <c r="F23">
-        <v>-1.974919155935837</v>
+        <v>-2.004401580168874</v>
       </c>
       <c r="G23">
-        <v>-2.385092595204804</v>
+        <v>-1.991526475257208</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>8.086522812365081</v>
       </c>
       <c r="E24">
-        <v>-24.51509989856143</v>
+        <v>-23.22104769460355</v>
       </c>
       <c r="F24">
-        <v>-1.454971989648852</v>
+        <v>-3.081535997703099</v>
       </c>
       <c r="G24">
-        <v>-2.815096680570034</v>
+        <v>-3.488810216041461</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.809955650351267</v>
       </c>
       <c r="E25">
-        <v>-24.23111929354042</v>
+        <v>-22.91597345765482</v>
       </c>
       <c r="F25">
-        <v>-1.414537719983402</v>
+        <v>-2.99359237238489</v>
       </c>
       <c r="G25">
-        <v>-2.292883706941289</v>
+        <v>-3.568986864846493</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>7.525126971117235</v>
       </c>
       <c r="E26">
-        <v>-24.55929780487629</v>
+        <v>-25.44699645070388</v>
       </c>
       <c r="F26">
-        <v>-0.87081309576646</v>
+        <v>-2.115971072182329</v>
       </c>
       <c r="G26">
-        <v>-2.721358743059818</v>
+        <v>-4.551998188175856</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>7.259664184415867</v>
       </c>
       <c r="E27">
-        <v>-24.78017865307442</v>
+        <v>-24.44874869740104</v>
       </c>
       <c r="F27">
-        <v>-1.263376407953146</v>
+        <v>-1.495280347469076</v>
       </c>
       <c r="G27">
-        <v>-2.268225326922062</v>
+        <v>-3.974158665449845</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>7.029170796829035</v>
       </c>
       <c r="E28">
-        <v>-24.2326997309691</v>
+        <v>-26.38987908078894</v>
       </c>
       <c r="F28">
-        <v>-1.418171767779484</v>
+        <v>-1.625875781990029</v>
       </c>
       <c r="G28">
-        <v>-3.000065702319052</v>
+        <v>-3.447699791123178</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.838064531899329</v>
       </c>
       <c r="E29">
-        <v>-23.7381948978055</v>
+        <v>-24.00737192129543</v>
       </c>
       <c r="F29">
-        <v>-1.100834984543229</v>
+        <v>-1.48234787557657</v>
       </c>
       <c r="G29">
-        <v>-3.484784157188022</v>
+        <v>-2.97076439379321</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.708665563852792</v>
       </c>
       <c r="E30">
-        <v>-23.04348170028879</v>
+        <v>-22.84533832008318</v>
       </c>
       <c r="F30">
-        <v>-1.319699592771693</v>
+        <v>-2.083889231039306</v>
       </c>
       <c r="G30">
-        <v>-3.755780245782562</v>
+        <v>-4.553993170884</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>6.654814642064983</v>
       </c>
       <c r="E31">
-        <v>-23.93677753998986</v>
+        <v>-24.24786106194678</v>
       </c>
       <c r="F31">
-        <v>-1.201968704016216</v>
+        <v>-2.31259567238043</v>
       </c>
       <c r="G31">
-        <v>-2.393682833247431</v>
+        <v>-4.171842420741711</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>6.674628155516459</v>
       </c>
       <c r="E32">
-        <v>-22.91151291075726</v>
+        <v>-23.96342308105099</v>
       </c>
       <c r="F32">
-        <v>-1.509672402725314</v>
+        <v>-2.084325780660582</v>
       </c>
       <c r="G32">
-        <v>-3.302699329189757</v>
+        <v>-4.761418872985856</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>6.779360813607729</v>
       </c>
       <c r="E33">
-        <v>-21.18908970804381</v>
+        <v>-23.28743965203001</v>
       </c>
       <c r="F33">
-        <v>-1.266887857373613</v>
+        <v>-2.479360112809819</v>
       </c>
       <c r="G33">
-        <v>-3.056378026722242</v>
+        <v>-4.503062049838299</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>6.97596588706993</v>
       </c>
       <c r="E34">
-        <v>-21.69861548949085</v>
+        <v>-22.86901771066928</v>
       </c>
       <c r="F34">
-        <v>-1.445510377174076</v>
+        <v>-2.834050467340511</v>
       </c>
       <c r="G34">
-        <v>-2.874004451226745</v>
+        <v>-3.36431082641145</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>7.253532949792696</v>
       </c>
       <c r="E35">
-        <v>-21.2183074223413</v>
+        <v>-20.36483951153769</v>
       </c>
       <c r="F35">
-        <v>-1.591878755411734</v>
+        <v>-2.249566853436221</v>
       </c>
       <c r="G35">
-        <v>-3.1739802886343</v>
+        <v>-3.821030617713679</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>7.602020836806275</v>
       </c>
       <c r="E36">
-        <v>-20.56885632253125</v>
+        <v>-21.80767020054357</v>
       </c>
       <c r="F36">
-        <v>-1.869644427816256</v>
+        <v>-2.090769650686959</v>
       </c>
       <c r="G36">
-        <v>-3.117444841165068</v>
+        <v>-4.13036778023033</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>8.019377864945756</v>
       </c>
       <c r="E37">
-        <v>-20.53337572868116</v>
+        <v>-20.80832655653087</v>
       </c>
       <c r="F37">
-        <v>-1.94576807866392</v>
+        <v>-2.411908640302063</v>
       </c>
       <c r="G37">
-        <v>-3.297964526479478</v>
+        <v>-3.746786417488123</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>8.487720670580416</v>
       </c>
       <c r="E38">
-        <v>-19.52547326879397</v>
+        <v>-19.24723929728869</v>
       </c>
       <c r="F38">
-        <v>-1.966564242311201</v>
+        <v>-2.734488989198038</v>
       </c>
       <c r="G38">
-        <v>-3.648106960309383</v>
+        <v>-3.790626818743864</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>8.98135973613727</v>
       </c>
       <c r="E39">
-        <v>-20.46287191685574</v>
+        <v>-19.31021678531337</v>
       </c>
       <c r="F39">
-        <v>-1.65181445047389</v>
+        <v>-3.11394587233763</v>
       </c>
       <c r="G39">
-        <v>-3.303280105405779</v>
+        <v>-3.790971347007606</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>9.494327969206719</v>
       </c>
       <c r="E40">
-        <v>-19.11266663520275</v>
+        <v>-19.79306079790721</v>
       </c>
       <c r="F40">
-        <v>-2.195170451196586</v>
+        <v>-2.904259574932186</v>
       </c>
       <c r="G40">
-        <v>-2.308197167959217</v>
+        <v>-2.038237945377463</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>10.00920726711713</v>
       </c>
       <c r="E41">
-        <v>-19.03087333767621</v>
+        <v>-17.9167464629911</v>
       </c>
       <c r="F41">
-        <v>-2.21790830803603</v>
+        <v>-2.703742476308329</v>
       </c>
       <c r="G41">
-        <v>-2.165362312255029</v>
+        <v>-4.028266008965089</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>10.49763509490907</v>
       </c>
       <c r="E42">
-        <v>-16.94895269738984</v>
+        <v>-16.85702014656012</v>
       </c>
       <c r="F42">
-        <v>-2.154476902534061</v>
+        <v>-3.706506896786617</v>
       </c>
       <c r="G42">
-        <v>-2.103524410745734</v>
+        <v>-4.00390950132933</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>10.95618911597777</v>
       </c>
       <c r="E43">
-        <v>-16.51166513331316</v>
+        <v>-15.64839760475695</v>
       </c>
       <c r="F43">
-        <v>-2.247461143498305</v>
+        <v>-2.672923067087173</v>
       </c>
       <c r="G43">
-        <v>-2.077924320138947</v>
+        <v>-4.390867241056205</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>11.37659935934612</v>
       </c>
       <c r="E44">
-        <v>-16.37384555536372</v>
+        <v>-16.46679701284516</v>
       </c>
       <c r="F44">
-        <v>-2.160646582950112</v>
+        <v>-2.990163759704703</v>
       </c>
       <c r="G44">
-        <v>-2.361172490036452</v>
+        <v>-4.345973567679883</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>11.73932011964412</v>
       </c>
       <c r="E45">
-        <v>-15.29866808561858</v>
+        <v>-16.5948758432041</v>
       </c>
       <c r="F45">
-        <v>-2.298069421604938</v>
+        <v>-2.827535357717493</v>
       </c>
       <c r="G45">
-        <v>-2.350101648494886</v>
+        <v>-3.294529087506739</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>12.0436384704258</v>
       </c>
       <c r="E46">
-        <v>-15.58070597529029</v>
+        <v>-13.95780051736941</v>
       </c>
       <c r="F46">
-        <v>-2.08398780676024</v>
+        <v>-2.841606006421445</v>
       </c>
       <c r="G46">
-        <v>-2.375757519868184</v>
+        <v>-4.030136305253972</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>12.29142179438653</v>
       </c>
       <c r="E47">
-        <v>-13.50563238770352</v>
+        <v>-14.02896548639995</v>
       </c>
       <c r="F47">
-        <v>-2.223434346980106</v>
+        <v>-2.705818365019744</v>
       </c>
       <c r="G47">
-        <v>-2.190775373232929</v>
+        <v>-2.129833245209362</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>12.47373627760911</v>
       </c>
       <c r="E48">
-        <v>-13.39471647383365</v>
+        <v>-12.94967163378183</v>
       </c>
       <c r="F48">
-        <v>-2.056952379835072</v>
+        <v>-2.508372852725469</v>
       </c>
       <c r="G48">
-        <v>-1.622556392119209</v>
+        <v>-2.493189158259151</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>12.58656564019712</v>
       </c>
       <c r="E49">
-        <v>-12.34430975691047</v>
+        <v>-11.26779638733306</v>
       </c>
       <c r="F49">
-        <v>-2.399677795599728</v>
+        <v>-3.220919582000353</v>
       </c>
       <c r="G49">
-        <v>-1.685988967306394</v>
+        <v>-2.169959303659811</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>12.64031387043873</v>
       </c>
       <c r="E50">
-        <v>-12.29023072031087</v>
+        <v>-10.11599713737814</v>
       </c>
       <c r="F50">
-        <v>-2.706472775267956</v>
+        <v>-2.504205336321984</v>
       </c>
       <c r="G50">
-        <v>-1.866085375039636</v>
+        <v>-3.255712236458509</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>12.63314242906593</v>
       </c>
       <c r="E51">
-        <v>-10.85194661920869</v>
+        <v>-7.821256332627291</v>
       </c>
       <c r="F51">
-        <v>-2.272057028422228</v>
+        <v>-3.066426576276037</v>
       </c>
       <c r="G51">
-        <v>-1.622582641891685</v>
+        <v>-2.219709184944112</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>12.55663179681813</v>
       </c>
       <c r="E52">
-        <v>-10.22104414893407</v>
+        <v>-10.40274464001783</v>
       </c>
       <c r="F52">
-        <v>-2.393110498830334</v>
+        <v>-2.58943440166122</v>
       </c>
       <c r="G52">
-        <v>-1.339354159323536</v>
+        <v>-3.616889418392826</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>12.42585318538177</v>
       </c>
       <c r="E53">
-        <v>-9.727259343137691</v>
+        <v>-8.941872510565398</v>
       </c>
       <c r="F53">
-        <v>-1.918260482319156</v>
+        <v>-2.651141974597963</v>
       </c>
       <c r="G53">
-        <v>-1.564505020289513</v>
+        <v>-3.105707911646934</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>12.2443659143673</v>
       </c>
       <c r="E54">
-        <v>-10.3407362454308</v>
+        <v>-10.05895195030351</v>
       </c>
       <c r="F54">
-        <v>-2.027558590914134</v>
+        <v>-2.440750736532736</v>
       </c>
       <c r="G54">
-        <v>-2.814036846006334</v>
+        <v>-3.795948960113284</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>12.00445629128207</v>
       </c>
       <c r="E55">
-        <v>-8.159646552850459</v>
+        <v>-11.1401160626868</v>
       </c>
       <c r="F55">
-        <v>-1.58729705530685</v>
+        <v>-2.727749392008862</v>
       </c>
       <c r="G55">
-        <v>-2.097742898357993</v>
+        <v>-2.383619326724614</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>11.72310715783134</v>
       </c>
       <c r="E56">
-        <v>-8.823380459680696</v>
+        <v>-6.666540745411426</v>
       </c>
       <c r="F56">
-        <v>-2.043473185456719</v>
+        <v>-2.760377955637731</v>
       </c>
       <c r="G56">
-        <v>-2.266978462729473</v>
+        <v>-3.302200583512721</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>11.4120354018829</v>
       </c>
       <c r="E57">
-        <v>-7.488635388289896</v>
+        <v>-7.161588995455943</v>
       </c>
       <c r="F57">
-        <v>-1.567431976620316</v>
+        <v>-2.452221968326704</v>
       </c>
       <c r="G57">
-        <v>-1.419140342762993</v>
+        <v>-2.12476703912158</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>11.07088955658715</v>
       </c>
       <c r="E58">
-        <v>-7.441675112830354</v>
+        <v>-6.372864677539996</v>
       </c>
       <c r="F58">
-        <v>-1.8612538943933</v>
+        <v>-2.939820559166966</v>
       </c>
       <c r="G58">
-        <v>-1.945979838790556</v>
+        <v>-3.535692309682807</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>10.71537580073513</v>
       </c>
       <c r="E59">
-        <v>-6.426033490864054</v>
+        <v>-7.375921670238981</v>
       </c>
       <c r="F59">
-        <v>-1.952367681762023</v>
+        <v>-2.594065803810272</v>
       </c>
       <c r="G59">
-        <v>-2.260458675490856</v>
+        <v>-2.642081148962074</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>10.36619711392426</v>
       </c>
       <c r="E60">
-        <v>-6.246597236784123</v>
+        <v>-4.58789872030661</v>
       </c>
       <c r="F60">
-        <v>-1.760048106956271</v>
+        <v>-2.165229939789801</v>
       </c>
       <c r="G60">
-        <v>-1.668335995316582</v>
+        <v>-3.830998968811272</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>10.03009800791449</v>
       </c>
       <c r="E61">
-        <v>-6.088413111222191</v>
+        <v>-4.938221469539989</v>
       </c>
       <c r="F61">
-        <v>-1.550481922824232</v>
+        <v>-2.55018966758619</v>
       </c>
       <c r="G61">
-        <v>-3.041884871094175</v>
+        <v>-3.86676100258766</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>9.71442870076093</v>
       </c>
       <c r="E62">
-        <v>-6.207385180351706</v>
+        <v>-6.0007463829077</v>
       </c>
       <c r="F62">
-        <v>-1.94005731378902</v>
+        <v>-2.443515826923281</v>
       </c>
       <c r="G62">
-        <v>-2.607966288408527</v>
+        <v>-3.260939222402704</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>9.44421981455092</v>
       </c>
       <c r="E63">
-        <v>-4.974589644295589</v>
+        <v>-4.52676432120306</v>
       </c>
       <c r="F63">
-        <v>-1.833814224175566</v>
+        <v>-3.204529504568562</v>
       </c>
       <c r="G63">
-        <v>-2.158816275243937</v>
+        <v>-3.863066347111725</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>9.226872956531345</v>
       </c>
       <c r="E64">
-        <v>-5.419385418276987</v>
+        <v>-3.938198554426144</v>
       </c>
       <c r="F64">
-        <v>-1.843756289743966</v>
+        <v>-2.807509575754815</v>
       </c>
       <c r="G64">
-        <v>-2.333013046613298</v>
+        <v>-5.074624595721092</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>9.058492989951953</v>
       </c>
       <c r="E65">
-        <v>-3.975947913754084</v>
+        <v>-3.877150196328739</v>
       </c>
       <c r="F65">
-        <v>-2.010776695700819</v>
+        <v>-2.720077053124133</v>
       </c>
       <c r="G65">
-        <v>-3.120000912759875</v>
+        <v>-2.453978560623787</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>8.957979427539446</v>
       </c>
       <c r="E66">
-        <v>-4.643440454010687</v>
+        <v>-3.597897318171739</v>
       </c>
       <c r="F66">
-        <v>-1.918910750730354</v>
+        <v>-2.924330088734615</v>
       </c>
       <c r="G66">
-        <v>-2.191625209616825</v>
+        <v>-2.511088221865922</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>8.927476366789822</v>
       </c>
       <c r="E67">
-        <v>-4.804079012484777</v>
+        <v>-1.623767944689947</v>
       </c>
       <c r="F67">
-        <v>-2.173627928519382</v>
+        <v>-2.822321613284272</v>
       </c>
       <c r="G67">
-        <v>-3.231513227457604</v>
+        <v>-3.319479496244757</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>8.951421100650919</v>
       </c>
       <c r="E68">
-        <v>-4.761217006002178</v>
+        <v>-4.076751745164826</v>
       </c>
       <c r="F68">
-        <v>-2.326495677399406</v>
+        <v>-3.441425186053761</v>
       </c>
       <c r="G68">
-        <v>-3.325539912465052</v>
+        <v>-3.013626991024237</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>9.03738829255348</v>
       </c>
       <c r="E69">
-        <v>-4.904719818831244</v>
+        <v>-3.481212128416097</v>
       </c>
       <c r="F69">
-        <v>-2.079469062577968</v>
+        <v>-3.720693516926961</v>
       </c>
       <c r="G69">
-        <v>-2.821872403090288</v>
+        <v>-3.299910290864229</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>9.184584614472039</v>
       </c>
       <c r="E70">
-        <v>-3.846410914764673</v>
+        <v>-2.841180254542007</v>
       </c>
       <c r="F70">
-        <v>-2.59039613621587</v>
+        <v>-3.169676774463175</v>
       </c>
       <c r="G70">
-        <v>-3.043587825083526</v>
+        <v>-3.232464781709843</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>9.37547674171163</v>
       </c>
       <c r="E71">
-        <v>-4.632336635743879</v>
+        <v>-3.959790318494716</v>
       </c>
       <c r="F71">
-        <v>-2.543933836960248</v>
+        <v>-3.542108273659625</v>
       </c>
       <c r="G71">
-        <v>-3.241711264064358</v>
+        <v>-3.676368121600881</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>9.607212685254797</v>
       </c>
       <c r="E72">
-        <v>-4.067337047702879</v>
+        <v>-3.035922750767863</v>
       </c>
       <c r="F72">
-        <v>-2.792602275974035</v>
+        <v>-3.191721287786476</v>
       </c>
       <c r="G72">
-        <v>-2.695207407231043</v>
+        <v>-3.177428852493276</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>9.882115313448049</v>
       </c>
       <c r="E73">
-        <v>-4.595329946153197</v>
+        <v>-4.318205450779802</v>
       </c>
       <c r="F73">
-        <v>-2.710205398784971</v>
+        <v>-3.780743526690703</v>
       </c>
       <c r="G73">
-        <v>-2.531271015678066</v>
+        <v>-3.487186011369536</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>10.1879312842742</v>
       </c>
       <c r="E74">
-        <v>-4.262903726198132</v>
+        <v>-2.956547658361417</v>
       </c>
       <c r="F74">
-        <v>-2.624881071194413</v>
+        <v>-3.68028824012061</v>
       </c>
       <c r="G74">
-        <v>-2.679575667721849</v>
+        <v>-3.27963562284842</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>10.51325209900473</v>
       </c>
       <c r="E75">
-        <v>-4.67251325713993</v>
+        <v>-1.887854963395259</v>
       </c>
       <c r="F75">
-        <v>-3.02586308129575</v>
+        <v>-3.446342374956779</v>
       </c>
       <c r="G75">
-        <v>-2.52238546769509</v>
+        <v>-3.22137425283892</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>10.86538852820721</v>
       </c>
       <c r="E76">
-        <v>-4.967153889974995</v>
+        <v>-5.017519577888304</v>
       </c>
       <c r="F76">
-        <v>-2.707558764933026</v>
+        <v>-4.060275278397993</v>
       </c>
       <c r="G76">
-        <v>-2.116534454228933</v>
+        <v>-2.521220634041487</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>11.23597348054541</v>
       </c>
       <c r="E77">
-        <v>-5.537442735656954</v>
+        <v>-6.157091948022519</v>
       </c>
       <c r="F77">
-        <v>-3.212477689798423</v>
+        <v>-4.052380937049314</v>
       </c>
       <c r="G77">
-        <v>-1.839425449869148</v>
+        <v>-2.413622816664176</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>11.60649125800342</v>
       </c>
       <c r="E78">
-        <v>-5.415925664135127</v>
+        <v>-6.628764215239441</v>
       </c>
       <c r="F78">
-        <v>-2.767668417149769</v>
+        <v>-4.232467182050524</v>
       </c>
       <c r="G78">
-        <v>-0.8065986208242943</v>
+        <v>-2.13652365596907</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>11.98220243721742</v>
       </c>
       <c r="E79">
-        <v>-7.247829254458017</v>
+        <v>-6.189434309385301</v>
       </c>
       <c r="F79">
-        <v>-3.508204024230444</v>
+        <v>-4.222788537316215</v>
       </c>
       <c r="G79">
-        <v>-1.398737707106366</v>
+        <v>-1.255233482204051</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>12.35444865327552</v>
       </c>
       <c r="E80">
-        <v>-7.717970897460345</v>
+        <v>-5.956933396883489</v>
       </c>
       <c r="F80">
-        <v>-3.55643737299325</v>
+        <v>-3.777046522972009</v>
       </c>
       <c r="G80">
-        <v>-0.903420906600389</v>
+        <v>-1.442978417392359</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>12.6967357509706</v>
       </c>
       <c r="E81">
-        <v>-7.871689947650716</v>
+        <v>-6.796530591801604</v>
       </c>
       <c r="F81">
-        <v>-3.598559027058203</v>
+        <v>-4.677016347334699</v>
       </c>
       <c r="G81">
-        <v>-0.5767982689085837</v>
+        <v>-0.2178260678622129</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>13.00624967248278</v>
       </c>
       <c r="E82">
-        <v>-8.387673333032692</v>
+        <v>-8.837821763291156</v>
       </c>
       <c r="F82">
-        <v>-3.720968534904691</v>
+        <v>-4.309948527071376</v>
       </c>
       <c r="G82">
-        <v>-0.8676851225964767</v>
+        <v>0.3943383135971499</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>13.27232130355062</v>
       </c>
       <c r="E83">
-        <v>-10.20970937849287</v>
+        <v>-10.03610579893482</v>
       </c>
       <c r="F83">
-        <v>-4.083126621571621</v>
+        <v>-4.723911882741984</v>
       </c>
       <c r="G83">
-        <v>0.164108121657152</v>
+        <v>0.9728636116290855</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>13.47017489039883</v>
       </c>
       <c r="E84">
-        <v>-10.98273347702422</v>
+        <v>-9.8331803501771</v>
       </c>
       <c r="F84">
-        <v>-3.997242317616771</v>
+        <v>-4.576750756899846</v>
       </c>
       <c r="G84">
-        <v>0.2488948867532035</v>
+        <v>-0.902918879701794</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>13.58780541324369</v>
       </c>
       <c r="E85">
-        <v>-11.29239505814273</v>
+        <v>-13.44961063575463</v>
       </c>
       <c r="F85">
-        <v>-4.079804868286395</v>
+        <v>-4.875952920954013</v>
       </c>
       <c r="G85">
-        <v>0.1414119121304729</v>
+        <v>0.5617528000031382</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>13.62091881133177</v>
       </c>
       <c r="E86">
-        <v>-12.2509869645604</v>
+        <v>-12.43516453092636</v>
       </c>
       <c r="F86">
-        <v>-4.44603603747289</v>
+        <v>-5.623966200579759</v>
       </c>
       <c r="G86">
-        <v>0.5946864207952848</v>
+        <v>2.051519262194704</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>13.55460606002392</v>
       </c>
       <c r="E87">
-        <v>-14.2668054697568</v>
+        <v>-14.03125236577382</v>
       </c>
       <c r="F87">
-        <v>-4.621804831570708</v>
+        <v>-5.01875517752262</v>
       </c>
       <c r="G87">
-        <v>0.5856072807403013</v>
+        <v>-0.3928858005017073</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>13.37502516930123</v>
       </c>
       <c r="E88">
-        <v>-15.93873618728473</v>
+        <v>-15.11634266512175</v>
       </c>
       <c r="F88">
-        <v>-4.694533832801699</v>
+        <v>-5.441575437463961</v>
       </c>
       <c r="G88">
-        <v>1.832583034862314</v>
+        <v>1.957833824229438</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>13.08988915162754</v>
       </c>
       <c r="E89">
-        <v>-17.26500848380718</v>
+        <v>-18.08260182352202</v>
       </c>
       <c r="F89">
-        <v>-5.011707427659602</v>
+        <v>-5.809628186569212</v>
       </c>
       <c r="G89">
-        <v>0.5592328218454847</v>
+        <v>2.298870868231884</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>12.69579794105352</v>
       </c>
       <c r="E90">
-        <v>-19.48927264757665</v>
+        <v>-17.01596958422935</v>
       </c>
       <c r="F90">
-        <v>-5.550536400525999</v>
+        <v>-5.871330789301539</v>
       </c>
       <c r="G90">
-        <v>0.8360530787080381</v>
+        <v>1.81594396033437</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>12.18556260265665</v>
       </c>
       <c r="E91">
-        <v>-20.70870012836212</v>
+        <v>-19.08911857036287</v>
       </c>
       <c r="F91">
-        <v>-6.085966581938711</v>
+        <v>-6.137162172533928</v>
       </c>
       <c r="G91">
-        <v>1.257913172162726</v>
+        <v>1.575637136985318</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>11.57436097400995</v>
       </c>
       <c r="E92">
-        <v>-22.2543769905562</v>
+        <v>-23.19215150196061</v>
       </c>
       <c r="F92">
-        <v>-5.78111495219745</v>
+        <v>-6.389225675348088</v>
       </c>
       <c r="G92">
-        <v>0.3903614730671029</v>
+        <v>0.02712368399345402</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>10.8695918027266</v>
       </c>
       <c r="E93">
-        <v>-23.79490950627756</v>
+        <v>-26.46017911128401</v>
       </c>
       <c r="F93">
-        <v>-6.158405654578721</v>
+        <v>-6.790510039551447</v>
       </c>
       <c r="G93">
-        <v>1.366948164583074</v>
+        <v>1.023735670686716</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>10.07208419741246</v>
       </c>
       <c r="E94">
-        <v>-25.95933441450968</v>
+        <v>-25.73260730636765</v>
       </c>
       <c r="F94">
-        <v>-6.445649506806075</v>
+        <v>-7.229459027008995</v>
       </c>
       <c r="G94">
-        <v>1.231578087926623</v>
+        <v>0.1764914518224964</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>9.200928778224437</v>
       </c>
       <c r="E95">
-        <v>-27.57419730259295</v>
+        <v>-27.38302777235914</v>
       </c>
       <c r="F95">
-        <v>-6.877962028816095</v>
+        <v>-7.396534933581836</v>
       </c>
       <c r="G95">
-        <v>0.2156692372422663</v>
+        <v>0.3787393863035498</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>8.267751751438995</v>
       </c>
       <c r="E96">
-        <v>-29.93712107624028</v>
+        <v>-29.82965359532725</v>
       </c>
       <c r="F96">
-        <v>-7.027069818054811</v>
+        <v>-6.960449198052064</v>
       </c>
       <c r="G96">
-        <v>0.9258830813409561</v>
+        <v>-0.8192280426065971</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>7.290816466082919</v>
       </c>
       <c r="E97">
-        <v>-32.62568741577919</v>
+        <v>-30.77862023024162</v>
       </c>
       <c r="F97">
-        <v>-7.241085163507287</v>
+        <v>-7.755953195064007</v>
       </c>
       <c r="G97">
-        <v>-0.2223410287280088</v>
+        <v>0.7913726847330794</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>6.270435513524306</v>
       </c>
       <c r="E98">
-        <v>-33.8061111499366</v>
+        <v>-32.3199361719663</v>
       </c>
       <c r="F98">
-        <v>-7.320230698640363</v>
+        <v>-8.203828255470421</v>
       </c>
       <c r="G98">
-        <v>-1.425256539749798</v>
+        <v>-1.308523801550993</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.258178224965496</v>
       </c>
       <c r="E99">
-        <v>-35.99214593613332</v>
+        <v>-34.83154786118149</v>
       </c>
       <c r="F99">
-        <v>-7.785738801766469</v>
+        <v>-7.894427231952986</v>
       </c>
       <c r="G99">
-        <v>-1.480568091577358</v>
+        <v>-1.278982963851312</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.231648640159342</v>
       </c>
       <c r="E100">
-        <v>-38.42286775838649</v>
+        <v>-36.89342321127291</v>
       </c>
       <c r="F100">
-        <v>-7.862747977367724</v>
+        <v>-8.276716303242749</v>
       </c>
       <c r="G100">
-        <v>-2.428053629082614</v>
+        <v>-3.970903693662876</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.269213259660095</v>
       </c>
       <c r="E101">
-        <v>-40.43987725224692</v>
+        <v>-39.77133637025754</v>
       </c>
       <c r="F101">
-        <v>-8.019396809257826</v>
+        <v>-7.613357201978697</v>
       </c>
       <c r="G101">
-        <v>-3.095703467112187</v>
+        <v>-3.230673234738386</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.296873367860345</v>
       </c>
       <c r="E102">
-        <v>-43.5101101738633</v>
+        <v>-43.17767263272321</v>
       </c>
       <c r="F102">
-        <v>-8.057908438181379</v>
+        <v>-8.464296788137085</v>
       </c>
       <c r="G102">
-        <v>-3.478375931482427</v>
+        <v>-3.741949896909502</v>
       </c>
     </row>
   </sheetData>
